--- a/officialtreedatabase_NFC.xlsx
+++ b/officialtreedatabase_NFC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livesalemstate-my.sharepoint.com/personal/s0422087_salemstate_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA046AD5-917E-4A35-B422-ABFFB660B64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{FA046AD5-917E-4A35-B422-ABFFB660B64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB720A32-ECDD-4BF6-A737-3920FFBD2F0C}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1740" windowWidth="21600" windowHeight="14460" xr2:uid="{C06BAD32-CBF9-4080-B573-E5CEA293F44F}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="13440" xr2:uid="{C06BAD32-CBF9-4080-B573-E5CEA293F44F}"/>
   </bookViews>
   <sheets>
     <sheet name="officialtreedatabase_NFC" sheetId="1" r:id="rId1"/>
@@ -1376,9 +1376,6 @@
     <t>AH22</t>
   </si>
   <si>
-    <t>AmandaMia</t>
-  </si>
-  <si>
     <t>AH23</t>
   </si>
   <si>
@@ -1998,6 +1995,9 @@
   </si>
   <si>
     <t>MD21</t>
+  </si>
+  <si>
+    <t>amanda &amp; mia</t>
   </si>
 </sst>
 </file>
@@ -14597,7 +14597,7 @@
         <v>425</v>
       </c>
       <c r="H382" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K382" t="s">
         <v>418</v>
@@ -14605,7 +14605,7 @@
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B383" t="s">
         <v>443</v>
@@ -14623,7 +14623,7 @@
         <v>425</v>
       </c>
       <c r="H383" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K383" t="s">
         <v>418</v>
@@ -14631,7 +14631,7 @@
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B384" t="s">
         <v>443</v>
@@ -14649,7 +14649,7 @@
         <v>425</v>
       </c>
       <c r="H384" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K384" t="s">
         <v>418</v>
@@ -14657,7 +14657,7 @@
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B385" t="s">
         <v>443</v>
@@ -14675,7 +14675,7 @@
         <v>425</v>
       </c>
       <c r="H385" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K385" t="s">
         <v>418</v>
@@ -14683,7 +14683,7 @@
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B386" t="s">
         <v>443</v>
@@ -14701,7 +14701,7 @@
         <v>425</v>
       </c>
       <c r="H386" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K386" t="s">
         <v>418</v>
@@ -14709,7 +14709,7 @@
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B387" t="s">
         <v>443</v>
@@ -14727,7 +14727,7 @@
         <v>425</v>
       </c>
       <c r="H387" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K387" t="s">
         <v>418</v>
@@ -14735,7 +14735,7 @@
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B388" t="s">
         <v>443</v>
@@ -14753,7 +14753,7 @@
         <v>425</v>
       </c>
       <c r="H388" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K388" t="s">
         <v>418</v>
@@ -14761,7 +14761,7 @@
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B389" t="s">
         <v>443</v>
@@ -14779,7 +14779,7 @@
         <v>425</v>
       </c>
       <c r="H389" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K389" t="s">
         <v>418</v>
@@ -14787,10 +14787,10 @@
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
+        <v>453</v>
+      </c>
+      <c r="B390" t="s">
         <v>454</v>
-      </c>
-      <c r="B390" t="s">
-        <v>455</v>
       </c>
       <c r="D390">
         <v>9.6</v>
@@ -14805,7 +14805,7 @@
         <v>425</v>
       </c>
       <c r="H390" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K390" t="s">
         <v>418</v>
@@ -14813,10 +14813,10 @@
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B391" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D391">
         <v>7.9</v>
@@ -14831,7 +14831,7 @@
         <v>425</v>
       </c>
       <c r="H391" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K391" t="s">
         <v>418</v>
@@ -14839,10 +14839,10 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B392" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D392">
         <v>9.6</v>
@@ -14857,7 +14857,7 @@
         <v>425</v>
       </c>
       <c r="H392" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K392" t="s">
         <v>418</v>
@@ -14865,10 +14865,10 @@
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B393" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D393">
         <v>5.9</v>
@@ -14883,7 +14883,7 @@
         <v>425</v>
       </c>
       <c r="H393" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K393" t="s">
         <v>418</v>
@@ -14891,10 +14891,10 @@
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B394" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D394">
         <v>5.8</v>
@@ -14909,7 +14909,7 @@
         <v>425</v>
       </c>
       <c r="H394" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K394" t="s">
         <v>418</v>
@@ -14917,10 +14917,10 @@
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B395" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D395">
         <v>8.1</v>
@@ -14935,7 +14935,7 @@
         <v>425</v>
       </c>
       <c r="H395" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K395" t="s">
         <v>418</v>
@@ -14943,10 +14943,10 @@
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B396" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D396">
         <v>7.8</v>
@@ -14961,7 +14961,7 @@
         <v>425</v>
       </c>
       <c r="H396" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K396" t="s">
         <v>418</v>
@@ -14969,10 +14969,10 @@
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B397" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D397">
         <v>9</v>
@@ -14987,7 +14987,7 @@
         <v>425</v>
       </c>
       <c r="H397" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K397" t="s">
         <v>418</v>
@@ -14995,10 +14995,10 @@
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B398" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D398">
         <v>6.4</v>
@@ -15013,7 +15013,7 @@
         <v>425</v>
       </c>
       <c r="H398" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K398" t="s">
         <v>418</v>
@@ -15021,10 +15021,10 @@
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B399" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D399">
         <v>5.2</v>
@@ -15039,7 +15039,7 @@
         <v>425</v>
       </c>
       <c r="H399" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K399" t="s">
         <v>418</v>
@@ -15047,10 +15047,10 @@
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>464</v>
+      </c>
+      <c r="B400" t="s">
         <v>465</v>
-      </c>
-      <c r="B400" t="s">
-        <v>466</v>
       </c>
       <c r="D400">
         <v>11.2</v>
@@ -15065,7 +15065,7 @@
         <v>425</v>
       </c>
       <c r="H400" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K400" t="s">
         <v>418</v>
@@ -15073,10 +15073,10 @@
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B401" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D401">
         <v>8.9</v>
@@ -15091,7 +15091,7 @@
         <v>425</v>
       </c>
       <c r="H401" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K401" t="s">
         <v>418</v>
@@ -15099,10 +15099,10 @@
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B402" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D402">
         <v>5.9</v>
@@ -15117,7 +15117,7 @@
         <v>425</v>
       </c>
       <c r="H402" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K402" t="s">
         <v>418</v>
@@ -15125,10 +15125,10 @@
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B403" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D403">
         <v>8</v>
@@ -15143,7 +15143,7 @@
         <v>425</v>
       </c>
       <c r="H403" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K403" t="s">
         <v>418</v>
@@ -15151,10 +15151,10 @@
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B404" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D404">
         <v>5.6</v>
@@ -15169,7 +15169,7 @@
         <v>425</v>
       </c>
       <c r="H404" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K404" t="s">
         <v>418</v>
@@ -15177,10 +15177,10 @@
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B405" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D405">
         <v>5.3</v>
@@ -15195,7 +15195,7 @@
         <v>425</v>
       </c>
       <c r="H405" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K405" t="s">
         <v>418</v>
@@ -15203,10 +15203,10 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B406" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D406">
         <v>6.3</v>
@@ -15221,7 +15221,7 @@
         <v>425</v>
       </c>
       <c r="H406" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K406" t="s">
         <v>418</v>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B407" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D407">
         <v>5.7</v>
@@ -15247,7 +15247,7 @@
         <v>425</v>
       </c>
       <c r="H407" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K407" t="s">
         <v>418</v>
@@ -15255,7 +15255,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B408" t="s">
         <v>99</v>
@@ -15273,7 +15273,7 @@
         <v>425</v>
       </c>
       <c r="H408" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K408" t="s">
         <v>418</v>
@@ -15281,7 +15281,7 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B409" t="s">
         <v>431</v>
@@ -15299,7 +15299,7 @@
         <v>416</v>
       </c>
       <c r="H409" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K409" t="s">
         <v>418</v>
@@ -15307,7 +15307,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B410" t="s">
         <v>431</v>
@@ -15325,7 +15325,7 @@
         <v>13</v>
       </c>
       <c r="H410" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K410" t="s">
         <v>418</v>
@@ -15333,7 +15333,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B411" t="s">
         <v>431</v>
@@ -15351,7 +15351,7 @@
         <v>13</v>
       </c>
       <c r="H411" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K411" t="s">
         <v>418</v>
@@ -15359,7 +15359,7 @@
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B412" t="s">
         <v>431</v>
@@ -15377,7 +15377,7 @@
         <v>13</v>
       </c>
       <c r="H412" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K412" t="s">
         <v>418</v>
@@ -15385,7 +15385,7 @@
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B413" t="s">
         <v>431</v>
@@ -15403,7 +15403,7 @@
         <v>425</v>
       </c>
       <c r="H413" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="K413" t="s">
         <v>418</v>
@@ -15411,7 +15411,7 @@
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B414" t="s">
         <v>431</v>
@@ -15429,7 +15429,7 @@
         <v>13</v>
       </c>
       <c r="H414" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K414" t="s">
         <v>418</v>
@@ -15437,7 +15437,7 @@
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B415" t="s">
         <v>431</v>
@@ -15455,7 +15455,7 @@
         <v>13</v>
       </c>
       <c r="H415" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K415" t="s">
         <v>418</v>
@@ -15463,7 +15463,7 @@
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B416" t="s">
         <v>431</v>
@@ -15481,7 +15481,7 @@
         <v>13</v>
       </c>
       <c r="H416" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K416" t="s">
         <v>418</v>
@@ -15489,10 +15489,10 @@
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
+        <v>485</v>
+      </c>
+      <c r="B417" t="s">
         <v>486</v>
-      </c>
-      <c r="B417" t="s">
-        <v>487</v>
       </c>
       <c r="D417">
         <v>3.1</v>
@@ -15507,7 +15507,7 @@
         <v>31</v>
       </c>
       <c r="H417" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K417" t="s">
         <v>418</v>
@@ -15515,10 +15515,10 @@
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>487</v>
+      </c>
+      <c r="B418" t="s">
         <v>488</v>
-      </c>
-      <c r="B418" t="s">
-        <v>489</v>
       </c>
       <c r="D418">
         <v>5.19</v>
@@ -15533,7 +15533,7 @@
         <v>13</v>
       </c>
       <c r="H418" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K418" t="s">
         <v>418</v>
@@ -15541,10 +15541,10 @@
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B419" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D419">
         <v>3.12</v>
@@ -15559,7 +15559,7 @@
         <v>13</v>
       </c>
       <c r="H419" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K419" t="s">
         <v>418</v>
@@ -15567,10 +15567,10 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B420" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D420">
         <v>6.1</v>
@@ -15585,7 +15585,7 @@
         <v>13</v>
       </c>
       <c r="H420" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K420" t="s">
         <v>418</v>
@@ -15593,10 +15593,10 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
+        <v>491</v>
+      </c>
+      <c r="B421" t="s">
         <v>492</v>
-      </c>
-      <c r="B421" t="s">
-        <v>493</v>
       </c>
       <c r="D421">
         <v>3.92</v>
@@ -15611,7 +15611,7 @@
         <v>13</v>
       </c>
       <c r="H421" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K421" t="s">
         <v>418</v>
@@ -15619,10 +15619,10 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
+        <v>493</v>
+      </c>
+      <c r="B422" t="s">
         <v>494</v>
-      </c>
-      <c r="B422" t="s">
-        <v>495</v>
       </c>
       <c r="D422">
         <v>42.33</v>
@@ -15637,7 +15637,7 @@
         <v>13</v>
       </c>
       <c r="H422" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K422" t="s">
         <v>418</v>
@@ -15645,10 +15645,10 @@
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
+        <v>495</v>
+      </c>
+      <c r="B423" t="s">
         <v>496</v>
-      </c>
-      <c r="B423" t="s">
-        <v>497</v>
       </c>
       <c r="D423">
         <v>4.0999999999999996</v>
@@ -15663,7 +15663,7 @@
         <v>31</v>
       </c>
       <c r="H423" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K423" t="s">
         <v>418</v>
@@ -15671,10 +15671,10 @@
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B424" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D424">
         <v>4.0999999999999996</v>
@@ -15689,7 +15689,7 @@
         <v>31</v>
       </c>
       <c r="H424" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K424" t="s">
         <v>418</v>
@@ -15697,10 +15697,10 @@
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B425" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D425">
         <v>3.6</v>
@@ -15715,7 +15715,7 @@
         <v>31</v>
       </c>
       <c r="H425" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="K425" t="s">
         <v>418</v>
@@ -15723,7 +15723,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B426" t="s">
         <v>99</v>
@@ -15741,7 +15741,7 @@
         <v>425</v>
       </c>
       <c r="H426" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K426" t="s">
         <v>418</v>
@@ -15749,7 +15749,7 @@
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B427" t="s">
         <v>99</v>
@@ -15767,7 +15767,7 @@
         <v>425</v>
       </c>
       <c r="H427" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K427" t="s">
         <v>418</v>
@@ -15775,7 +15775,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B428" t="s">
         <v>99</v>
@@ -15793,7 +15793,7 @@
         <v>425</v>
       </c>
       <c r="H428" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K428" t="s">
         <v>418</v>
@@ -15801,10 +15801,10 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B429" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D429">
         <v>4.4000000000000004</v>
@@ -15819,7 +15819,7 @@
         <v>13</v>
       </c>
       <c r="H429" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K429" t="s">
         <v>418</v>
@@ -15827,10 +15827,10 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B430" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D430">
         <v>3.4</v>
@@ -15845,7 +15845,7 @@
         <v>13</v>
       </c>
       <c r="H430" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K430" t="s">
         <v>418</v>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B431" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D431">
         <v>4.3</v>
@@ -15871,7 +15871,7 @@
         <v>13</v>
       </c>
       <c r="H431" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K431" t="s">
         <v>418</v>
@@ -15879,7 +15879,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B432" t="s">
         <v>233</v>
@@ -15897,7 +15897,7 @@
         <v>31</v>
       </c>
       <c r="H432" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K432" t="s">
         <v>418</v>
@@ -15905,7 +15905,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B433" t="s">
         <v>233</v>
@@ -15923,7 +15923,7 @@
         <v>31</v>
       </c>
       <c r="H433" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="K433" t="s">
         <v>418</v>
@@ -15931,10 +15931,10 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
+        <v>510</v>
+      </c>
+      <c r="B434" t="s">
         <v>511</v>
-      </c>
-      <c r="B434" t="s">
-        <v>512</v>
       </c>
       <c r="D434">
         <v>2.1</v>
@@ -15949,7 +15949,7 @@
         <v>28</v>
       </c>
       <c r="H434" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K434" t="s">
         <v>418</v>
@@ -15957,10 +15957,10 @@
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B435" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D435">
         <v>4.2</v>
@@ -15975,7 +15975,7 @@
         <v>425</v>
       </c>
       <c r="H435" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K435" t="s">
         <v>418</v>
@@ -15983,10 +15983,10 @@
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B436" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D436">
         <v>2.5</v>
@@ -16001,7 +16001,7 @@
         <v>13</v>
       </c>
       <c r="H436" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K436" t="s">
         <v>418</v>
@@ -16009,10 +16009,10 @@
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B437" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D437">
         <v>5.8</v>
@@ -16027,7 +16027,7 @@
         <v>425</v>
       </c>
       <c r="H437" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K437" t="s">
         <v>418</v>
@@ -16035,10 +16035,10 @@
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B438" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D438">
         <v>5.0999999999999996</v>
@@ -16053,7 +16053,7 @@
         <v>425</v>
       </c>
       <c r="H438" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K438" t="s">
         <v>418</v>
@@ -16061,7 +16061,7 @@
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B439" t="s">
         <v>99</v>
@@ -16079,7 +16079,7 @@
         <v>425</v>
       </c>
       <c r="H439" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K439" t="s">
         <v>418</v>
@@ -16087,7 +16087,7 @@
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B440" t="s">
         <v>99</v>
@@ -16105,7 +16105,7 @@
         <v>425</v>
       </c>
       <c r="H440" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K440" t="s">
         <v>418</v>
@@ -16113,7 +16113,7 @@
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B441" t="s">
         <v>99</v>
@@ -16131,7 +16131,7 @@
         <v>425</v>
       </c>
       <c r="H441" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K441" t="s">
         <v>418</v>
@@ -16139,7 +16139,7 @@
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B442" t="s">
         <v>99</v>
@@ -16157,7 +16157,7 @@
         <v>425</v>
       </c>
       <c r="H442" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K442" t="s">
         <v>418</v>
@@ -16165,7 +16165,7 @@
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B443" t="s">
         <v>99</v>
@@ -16183,7 +16183,7 @@
         <v>425</v>
       </c>
       <c r="H443" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K443" t="s">
         <v>418</v>
@@ -16191,7 +16191,7 @@
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B444" t="s">
         <v>99</v>
@@ -16209,7 +16209,7 @@
         <v>425</v>
       </c>
       <c r="H444" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K444" t="s">
         <v>418</v>
@@ -16217,7 +16217,7 @@
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B445" t="s">
         <v>99</v>
@@ -16235,7 +16235,7 @@
         <v>425</v>
       </c>
       <c r="H445" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K445" t="s">
         <v>418</v>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B446" t="s">
         <v>99</v>
@@ -16261,7 +16261,7 @@
         <v>425</v>
       </c>
       <c r="H446" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K446" t="s">
         <v>418</v>
@@ -16269,10 +16269,10 @@
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B447" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D447">
         <v>3</v>
@@ -16287,7 +16287,7 @@
         <v>425</v>
       </c>
       <c r="H447" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K447" t="s">
         <v>418</v>
@@ -16295,10 +16295,10 @@
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
+        <v>526</v>
+      </c>
+      <c r="B448" t="s">
         <v>527</v>
-      </c>
-      <c r="B448" t="s">
-        <v>528</v>
       </c>
       <c r="D448">
         <v>3.9</v>
@@ -16313,7 +16313,7 @@
         <v>416</v>
       </c>
       <c r="H448" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K448" t="s">
         <v>418</v>
@@ -16321,10 +16321,10 @@
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B449" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D449">
         <v>4.5999999999999996</v>
@@ -16339,7 +16339,7 @@
         <v>425</v>
       </c>
       <c r="H449" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K449" t="s">
         <v>418</v>
@@ -16347,10 +16347,10 @@
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B450" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D450">
         <v>4.7</v>
@@ -16365,7 +16365,7 @@
         <v>425</v>
       </c>
       <c r="H450" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K450" t="s">
         <v>418</v>
@@ -16373,10 +16373,10 @@
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B451" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D451">
         <v>5.7</v>
@@ -16391,7 +16391,7 @@
         <v>425</v>
       </c>
       <c r="H451" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K451" t="s">
         <v>418</v>
@@ -16399,10 +16399,10 @@
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
+        <v>531</v>
+      </c>
+      <c r="B452" t="s">
         <v>532</v>
-      </c>
-      <c r="B452" t="s">
-        <v>533</v>
       </c>
       <c r="D452">
         <v>4.2</v>
@@ -16417,7 +16417,7 @@
         <v>425</v>
       </c>
       <c r="H452" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K452" t="s">
         <v>418</v>
@@ -16425,10 +16425,10 @@
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B453" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D453">
         <v>5.7</v>
@@ -16443,7 +16443,7 @@
         <v>13</v>
       </c>
       <c r="H453" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K453" t="s">
         <v>418</v>
@@ -16451,10 +16451,10 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B454" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D454">
         <v>5.7</v>
@@ -16469,7 +16469,7 @@
         <v>13</v>
       </c>
       <c r="H454" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K454" t="s">
         <v>418</v>
@@ -16477,10 +16477,10 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B455" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D455">
         <v>5.7</v>
@@ -16495,7 +16495,7 @@
         <v>13</v>
       </c>
       <c r="H455" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K455" t="s">
         <v>418</v>
@@ -16503,10 +16503,10 @@
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B456" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D456">
         <v>5.8</v>
@@ -16521,7 +16521,7 @@
         <v>13</v>
       </c>
       <c r="H456" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K456" t="s">
         <v>418</v>
@@ -16529,10 +16529,10 @@
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B457" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D457">
         <v>2.1</v>
@@ -16547,7 +16547,7 @@
         <v>13</v>
       </c>
       <c r="H457" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K457" t="s">
         <v>418</v>
@@ -16555,10 +16555,10 @@
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B458" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D458">
         <v>0</v>
@@ -16573,7 +16573,7 @@
         <v>13</v>
       </c>
       <c r="H458" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K458" t="s">
         <v>418</v>
@@ -16581,10 +16581,10 @@
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>540</v>
+      </c>
+      <c r="B459" t="s">
         <v>541</v>
-      </c>
-      <c r="B459" t="s">
-        <v>542</v>
       </c>
       <c r="D459">
         <v>8.3000000000000007</v>
@@ -16599,7 +16599,7 @@
         <v>13</v>
       </c>
       <c r="H459" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K459" t="s">
         <v>418</v>
@@ -16607,10 +16607,10 @@
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B460" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D460">
         <v>7</v>
@@ -16625,7 +16625,7 @@
         <v>425</v>
       </c>
       <c r="H460" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K460" t="s">
         <v>418</v>
@@ -16633,10 +16633,10 @@
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
+        <v>544</v>
+      </c>
+      <c r="B461" t="s">
         <v>545</v>
-      </c>
-      <c r="B461" t="s">
-        <v>546</v>
       </c>
       <c r="D461">
         <v>7.3</v>
@@ -16651,7 +16651,7 @@
         <v>13</v>
       </c>
       <c r="H461" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K461" t="s">
         <v>418</v>
@@ -16659,10 +16659,10 @@
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B462" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D462">
         <v>6.7</v>
@@ -16677,7 +16677,7 @@
         <v>425</v>
       </c>
       <c r="H462" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K462" t="s">
         <v>418</v>
@@ -16685,10 +16685,10 @@
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B463" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D463">
         <v>8.3000000000000007</v>
@@ -16703,7 +16703,7 @@
         <v>425</v>
       </c>
       <c r="H463" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K463" t="s">
         <v>418</v>
@@ -16711,10 +16711,10 @@
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B464" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D464">
         <v>5.5</v>
@@ -16729,7 +16729,7 @@
         <v>425</v>
       </c>
       <c r="H464" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K464" t="s">
         <v>418</v>
@@ -16737,10 +16737,10 @@
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B465" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D465">
         <v>6.05</v>
@@ -16755,7 +16755,7 @@
         <v>425</v>
       </c>
       <c r="H465" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K465" t="s">
         <v>418</v>
@@ -16763,10 +16763,10 @@
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
+        <v>551</v>
+      </c>
+      <c r="B466" t="s">
         <v>552</v>
-      </c>
-      <c r="B466" t="s">
-        <v>553</v>
       </c>
       <c r="D466">
         <v>4.4000000000000004</v>
@@ -16781,7 +16781,7 @@
         <v>13</v>
       </c>
       <c r="H466" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K466" t="s">
         <v>418</v>
@@ -16789,10 +16789,10 @@
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B467" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D467">
         <v>6.4</v>
@@ -16807,7 +16807,7 @@
         <v>13</v>
       </c>
       <c r="H467" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K467" t="s">
         <v>418</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B468" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D468">
         <v>7.3</v>
@@ -16833,7 +16833,7 @@
         <v>31</v>
       </c>
       <c r="H468" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K468" t="s">
         <v>418</v>
@@ -16841,10 +16841,10 @@
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B469" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D469">
         <v>6</v>
@@ -16859,7 +16859,7 @@
         <v>416</v>
       </c>
       <c r="H469" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K469" t="s">
         <v>418</v>
@@ -16867,7 +16867,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B470" t="s">
         <v>431</v>
@@ -16885,7 +16885,7 @@
         <v>425</v>
       </c>
       <c r="H470" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K470" t="s">
         <v>418</v>
@@ -16893,7 +16893,7 @@
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B471" t="s">
         <v>431</v>
@@ -16911,7 +16911,7 @@
         <v>425</v>
       </c>
       <c r="H471" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K471" t="s">
         <v>418</v>
@@ -16919,7 +16919,7 @@
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B472" t="s">
         <v>431</v>
@@ -16937,7 +16937,7 @@
         <v>425</v>
       </c>
       <c r="H472" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K472" t="s">
         <v>418</v>
@@ -16945,10 +16945,10 @@
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B473" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D473">
         <v>5.7</v>
@@ -16963,7 +16963,7 @@
         <v>31</v>
       </c>
       <c r="H473" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K473" t="s">
         <v>418</v>
@@ -16971,10 +16971,10 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B474" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D474">
         <v>8</v>
@@ -16989,7 +16989,7 @@
         <v>31</v>
       </c>
       <c r="H474" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K474" t="s">
         <v>418</v>
@@ -16997,10 +16997,10 @@
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B475" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D475">
         <v>5.3</v>
@@ -17015,7 +17015,7 @@
         <v>425</v>
       </c>
       <c r="H475" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K475" t="s">
         <v>418</v>
@@ -17023,10 +17023,10 @@
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B476" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D476">
         <v>4.5</v>
@@ -17041,7 +17041,7 @@
         <v>416</v>
       </c>
       <c r="H476" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K476" t="s">
         <v>418</v>
@@ -17049,10 +17049,10 @@
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B477" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D477">
         <v>4.0999999999999996</v>
@@ -17067,7 +17067,7 @@
         <v>425</v>
       </c>
       <c r="H477" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K477" t="s">
         <v>418</v>
@@ -17075,10 +17075,10 @@
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B478" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D478">
         <v>4.0999999999999996</v>
@@ -17093,7 +17093,7 @@
         <v>425</v>
       </c>
       <c r="H478" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="K478" t="s">
         <v>418</v>
@@ -17101,10 +17101,10 @@
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B479" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D479">
         <v>3.9</v>
@@ -17119,7 +17119,7 @@
         <v>425</v>
       </c>
       <c r="H479" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K479" t="s">
         <v>418</v>
@@ -17127,10 +17127,10 @@
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B480" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D480">
         <v>6.8</v>
@@ -17145,7 +17145,7 @@
         <v>425</v>
       </c>
       <c r="H480" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K480" t="s">
         <v>418</v>
@@ -17153,10 +17153,10 @@
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B481" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D481">
         <v>6.8</v>
@@ -17171,7 +17171,7 @@
         <v>425</v>
       </c>
       <c r="H481" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K481" t="s">
         <v>418</v>
@@ -17179,7 +17179,7 @@
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B482" t="s">
         <v>431</v>
@@ -17197,7 +17197,7 @@
         <v>425</v>
       </c>
       <c r="H482" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K482" t="s">
         <v>418</v>
@@ -17205,10 +17205,10 @@
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B483" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D483">
         <v>5.7</v>
@@ -17223,7 +17223,7 @@
         <v>425</v>
       </c>
       <c r="H483" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K483" t="s">
         <v>418</v>
@@ -17231,7 +17231,7 @@
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B484" t="s">
         <v>431</v>
@@ -17249,7 +17249,7 @@
         <v>416</v>
       </c>
       <c r="H484" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K484" t="s">
         <v>418</v>
@@ -17257,7 +17257,7 @@
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B485" t="s">
         <v>431</v>
@@ -17275,7 +17275,7 @@
         <v>416</v>
       </c>
       <c r="H485" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K485" t="s">
         <v>418</v>
@@ -17283,10 +17283,10 @@
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B486" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D486">
         <v>5.9</v>
@@ -17301,7 +17301,7 @@
         <v>416</v>
       </c>
       <c r="H486" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K486" t="s">
         <v>418</v>
@@ -17309,10 +17309,10 @@
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B487" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D487">
         <v>6.4</v>
@@ -17327,7 +17327,7 @@
         <v>416</v>
       </c>
       <c r="H487" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K487" t="s">
         <v>418</v>
@@ -17335,10 +17335,10 @@
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
+        <v>577</v>
+      </c>
+      <c r="B488" t="s">
         <v>578</v>
-      </c>
-      <c r="B488" t="s">
-        <v>579</v>
       </c>
       <c r="D488">
         <v>4.7</v>
@@ -17353,7 +17353,7 @@
         <v>416</v>
       </c>
       <c r="H488" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K488" t="s">
         <v>418</v>
@@ -17361,10 +17361,10 @@
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B489" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D489">
         <v>4.8</v>
@@ -17379,7 +17379,7 @@
         <v>416</v>
       </c>
       <c r="H489" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K489" t="s">
         <v>418</v>
@@ -17387,10 +17387,10 @@
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B490" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D490">
         <v>4.5999999999999996</v>
@@ -17405,7 +17405,7 @@
         <v>13</v>
       </c>
       <c r="H490" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K490" t="s">
         <v>418</v>
@@ -17413,10 +17413,10 @@
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B491" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D491">
         <v>5.6</v>
@@ -17431,7 +17431,7 @@
         <v>416</v>
       </c>
       <c r="H491" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K491" t="s">
         <v>418</v>
@@ -17439,10 +17439,10 @@
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B492" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D492">
         <v>5.9</v>
@@ -17457,7 +17457,7 @@
         <v>416</v>
       </c>
       <c r="H492" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K492" t="s">
         <v>418</v>
@@ -17465,10 +17465,10 @@
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B493" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D493">
         <v>4.5999999999999996</v>
@@ -17483,7 +17483,7 @@
         <v>416</v>
       </c>
       <c r="H493" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K493" t="s">
         <v>418</v>
@@ -17491,10 +17491,10 @@
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
+        <v>584</v>
+      </c>
+      <c r="B494" t="s">
         <v>585</v>
-      </c>
-      <c r="B494" t="s">
-        <v>586</v>
       </c>
       <c r="D494">
         <v>6.7</v>
@@ -17509,7 +17509,7 @@
         <v>13</v>
       </c>
       <c r="H494" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K494" t="s">
         <v>418</v>
@@ -17517,10 +17517,10 @@
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B495" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D495">
         <v>5.4</v>
@@ -17535,7 +17535,7 @@
         <v>425</v>
       </c>
       <c r="H495" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K495" t="s">
         <v>418</v>
@@ -17543,10 +17543,10 @@
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B496" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D496">
         <v>5.8</v>
@@ -17561,7 +17561,7 @@
         <v>425</v>
       </c>
       <c r="H496" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K496" t="s">
         <v>418</v>
@@ -17569,10 +17569,10 @@
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B497" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D497">
         <v>6.8</v>
@@ -17587,7 +17587,7 @@
         <v>425</v>
       </c>
       <c r="H497" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K497" t="s">
         <v>418</v>
@@ -17595,10 +17595,10 @@
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B498" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D498">
         <v>7.9</v>
@@ -17613,7 +17613,7 @@
         <v>13</v>
       </c>
       <c r="H498" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K498" t="s">
         <v>418</v>
@@ -17621,10 +17621,10 @@
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B499" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D499">
         <v>1.2</v>
@@ -17639,7 +17639,7 @@
         <v>425</v>
       </c>
       <c r="H499" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K499" t="s">
         <v>418</v>
@@ -17647,10 +17647,10 @@
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B500" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D500">
         <v>7.6</v>
@@ -17665,7 +17665,7 @@
         <v>425</v>
       </c>
       <c r="H500" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K500" t="s">
         <v>418</v>
@@ -17673,10 +17673,10 @@
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B501" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D501">
         <v>4.0999999999999996</v>
@@ -17688,10 +17688,10 @@
         <v>0</v>
       </c>
       <c r="G501" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H501" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K501" t="s">
         <v>418</v>
@@ -17699,10 +17699,10 @@
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B502" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D502">
         <v>6.3</v>
@@ -17717,7 +17717,7 @@
         <v>425</v>
       </c>
       <c r="H502" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K502" t="s">
         <v>418</v>
@@ -17725,10 +17725,10 @@
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B503" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D503">
         <v>7.6</v>
@@ -17743,7 +17743,7 @@
         <v>425</v>
       </c>
       <c r="H503" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K503" t="s">
         <v>418</v>
@@ -17751,10 +17751,10 @@
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B504" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D504">
         <v>7.1</v>
@@ -17769,7 +17769,7 @@
         <v>425</v>
       </c>
       <c r="H504" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K504" t="s">
         <v>418</v>
@@ -17777,10 +17777,10 @@
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B505" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D505">
         <v>4.0999999999999996</v>
@@ -17795,7 +17795,7 @@
         <v>416</v>
       </c>
       <c r="H505" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K505" t="s">
         <v>418</v>
@@ -17803,10 +17803,10 @@
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B506" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D506">
         <v>4.3</v>
@@ -17821,7 +17821,7 @@
         <v>425</v>
       </c>
       <c r="H506" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K506" t="s">
         <v>418</v>
@@ -17829,10 +17829,10 @@
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B507" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D507">
         <v>0</v>
@@ -17847,7 +17847,7 @@
         <v>416</v>
       </c>
       <c r="H507" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K507" t="s">
         <v>418</v>
@@ -17855,10 +17855,10 @@
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B508" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D508">
         <v>5.8</v>
@@ -17873,7 +17873,7 @@
         <v>425</v>
       </c>
       <c r="H508" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K508" t="s">
         <v>418</v>
@@ -17881,10 +17881,10 @@
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B509" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D509">
         <v>3.5</v>
@@ -17899,7 +17899,7 @@
         <v>425</v>
       </c>
       <c r="H509" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K509" t="s">
         <v>418</v>
@@ -17907,10 +17907,10 @@
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B510" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D510">
         <v>7.1</v>
@@ -17925,7 +17925,7 @@
         <v>425</v>
       </c>
       <c r="H510" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K510" t="s">
         <v>418</v>
@@ -17933,10 +17933,10 @@
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
+        <v>607</v>
+      </c>
+      <c r="B511" t="s">
         <v>608</v>
-      </c>
-      <c r="B511" t="s">
-        <v>609</v>
       </c>
       <c r="D511">
         <v>2.38</v>
@@ -17951,7 +17951,7 @@
         <v>416</v>
       </c>
       <c r="H511" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K511" t="s">
         <v>418</v>
@@ -17959,10 +17959,10 @@
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B512" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D512">
         <v>2.38</v>
@@ -17977,7 +17977,7 @@
         <v>13</v>
       </c>
       <c r="H512" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K512" t="s">
         <v>418</v>
@@ -17985,10 +17985,10 @@
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B513" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D513">
         <v>2.38</v>
@@ -18003,7 +18003,7 @@
         <v>31</v>
       </c>
       <c r="H513" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K513" t="s">
         <v>418</v>
@@ -18011,10 +18011,10 @@
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B514" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D514">
         <v>2.38</v>
@@ -18029,7 +18029,7 @@
         <v>31</v>
       </c>
       <c r="H514" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K514" t="s">
         <v>418</v>
@@ -18037,10 +18037,10 @@
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
+        <v>615</v>
+      </c>
+      <c r="B515" t="s">
         <v>616</v>
-      </c>
-      <c r="B515" t="s">
-        <v>617</v>
       </c>
       <c r="D515">
         <v>5.9</v>
@@ -18055,7 +18055,7 @@
         <v>425</v>
       </c>
       <c r="H515" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K515" t="s">
         <v>418</v>
@@ -18063,10 +18063,10 @@
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
+        <v>617</v>
+      </c>
+      <c r="B516" t="s">
         <v>618</v>
-      </c>
-      <c r="B516" t="s">
-        <v>619</v>
       </c>
       <c r="D516">
         <v>1.5</v>
@@ -18081,7 +18081,7 @@
         <v>13</v>
       </c>
       <c r="H516" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K516" t="s">
         <v>418</v>
@@ -18089,10 +18089,10 @@
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B517" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D517">
         <v>2.8</v>
@@ -18107,7 +18107,7 @@
         <v>13</v>
       </c>
       <c r="H517" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K517" t="s">
         <v>418</v>
@@ -18115,10 +18115,10 @@
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
+        <v>620</v>
+      </c>
+      <c r="B518" t="s">
         <v>621</v>
-      </c>
-      <c r="B518" t="s">
-        <v>622</v>
       </c>
       <c r="D518">
         <v>12.1</v>
@@ -18133,7 +18133,7 @@
         <v>416</v>
       </c>
       <c r="H518" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K518" t="s">
         <v>418</v>
@@ -18141,10 +18141,10 @@
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B519" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D519">
         <v>3.6</v>
@@ -18159,7 +18159,7 @@
         <v>416</v>
       </c>
       <c r="H519" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K519" t="s">
         <v>418</v>
@@ -18167,10 +18167,10 @@
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B520" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D520">
         <v>2.5</v>
@@ -18185,7 +18185,7 @@
         <v>425</v>
       </c>
       <c r="H520" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K520" t="s">
         <v>418</v>
@@ -18193,10 +18193,10 @@
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
+        <v>624</v>
+      </c>
+      <c r="B521" t="s">
         <v>625</v>
-      </c>
-      <c r="B521" t="s">
-        <v>626</v>
       </c>
       <c r="D521">
         <v>8.6999999999999993</v>
@@ -18211,7 +18211,7 @@
         <v>416</v>
       </c>
       <c r="H521" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K521" t="s">
         <v>418</v>
@@ -18219,10 +18219,10 @@
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B522" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D522">
         <v>9.5</v>
@@ -18237,7 +18237,7 @@
         <v>416</v>
       </c>
       <c r="H522" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K522" t="s">
         <v>418</v>
@@ -18245,10 +18245,10 @@
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B523" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D523">
         <v>10.9</v>
@@ -18263,7 +18263,7 @@
         <v>425</v>
       </c>
       <c r="H523" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K523" t="s">
         <v>418</v>
@@ -18271,10 +18271,10 @@
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B524" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D524">
         <v>10.3</v>
@@ -18289,7 +18289,7 @@
         <v>425</v>
       </c>
       <c r="H524" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K524" t="s">
         <v>418</v>
@@ -18297,10 +18297,10 @@
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B525" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D525">
         <v>10.199999999999999</v>
@@ -18315,7 +18315,7 @@
         <v>425</v>
       </c>
       <c r="H525" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K525" t="s">
         <v>418</v>
@@ -18323,10 +18323,10 @@
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B526" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D526">
         <v>10</v>
@@ -18341,7 +18341,7 @@
         <v>425</v>
       </c>
       <c r="H526" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K526" t="s">
         <v>418</v>
@@ -18349,10 +18349,10 @@
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B527" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D527">
         <v>9.5</v>
@@ -18367,7 +18367,7 @@
         <v>425</v>
       </c>
       <c r="H527" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K527" t="s">
         <v>418</v>
@@ -18375,10 +18375,10 @@
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B528" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D528">
         <v>11.1</v>
@@ -18393,7 +18393,7 @@
         <v>425</v>
       </c>
       <c r="H528" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K528" t="s">
         <v>418</v>
@@ -18401,10 +18401,10 @@
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
+        <v>633</v>
+      </c>
+      <c r="B529" t="s">
         <v>634</v>
-      </c>
-      <c r="B529" t="s">
-        <v>635</v>
       </c>
       <c r="D529">
         <v>11.4</v>
@@ -18419,7 +18419,7 @@
         <v>416</v>
       </c>
       <c r="H529" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K529" t="s">
         <v>418</v>
@@ -18427,10 +18427,10 @@
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
+        <v>635</v>
+      </c>
+      <c r="B530" t="s">
         <v>636</v>
-      </c>
-      <c r="B530" t="s">
-        <v>637</v>
       </c>
       <c r="D530">
         <v>9.6999999999999993</v>
@@ -18445,7 +18445,7 @@
         <v>416</v>
       </c>
       <c r="H530" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K530" t="s">
         <v>418</v>
@@ -18453,10 +18453,10 @@
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B531" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D531">
         <v>11.4</v>
@@ -18471,7 +18471,7 @@
         <v>425</v>
       </c>
       <c r="H531" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K531" t="s">
         <v>418</v>
@@ -18479,10 +18479,10 @@
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B532" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D532">
         <v>11.3</v>
@@ -18497,7 +18497,7 @@
         <v>425</v>
       </c>
       <c r="H532" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="K532" t="s">
         <v>418</v>
@@ -18505,10 +18505,10 @@
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B533" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D533">
         <v>8.6</v>
@@ -18523,7 +18523,7 @@
         <v>425</v>
       </c>
       <c r="H533" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K533" t="s">
         <v>418</v>
@@ -18531,10 +18531,10 @@
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B534" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D534">
         <v>7.2</v>
@@ -18546,10 +18546,10 @@
         <v>3</v>
       </c>
       <c r="G534" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H534" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K534" t="s">
         <v>418</v>
@@ -18557,10 +18557,10 @@
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B535" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D535">
         <v>11.9</v>
@@ -18575,7 +18575,7 @@
         <v>425</v>
       </c>
       <c r="H535" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K535" t="s">
         <v>418</v>
@@ -18583,10 +18583,10 @@
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B536" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D536">
         <v>12</v>
@@ -18601,7 +18601,7 @@
         <v>416</v>
       </c>
       <c r="H536" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K536" t="s">
         <v>418</v>
@@ -18609,10 +18609,10 @@
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B537" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D537">
         <v>11.4</v>
@@ -18627,7 +18627,7 @@
         <v>425</v>
       </c>
       <c r="H537" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K537" t="s">
         <v>418</v>
@@ -18635,10 +18635,10 @@
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B538" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D538">
         <v>9.5</v>
@@ -18653,7 +18653,7 @@
         <v>425</v>
       </c>
       <c r="H538" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K538" t="s">
         <v>418</v>
@@ -18661,10 +18661,10 @@
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B539" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D539">
         <v>11.9</v>
@@ -18679,7 +18679,7 @@
         <v>425</v>
       </c>
       <c r="H539" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K539" t="s">
         <v>418</v>
@@ -18687,10 +18687,10 @@
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B540" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D540">
         <v>12.5</v>
@@ -18705,7 +18705,7 @@
         <v>425</v>
       </c>
       <c r="H540" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K540" t="s">
         <v>418</v>
@@ -18713,10 +18713,10 @@
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
+        <v>648</v>
+      </c>
+      <c r="B541" t="s">
         <v>649</v>
-      </c>
-      <c r="B541" t="s">
-        <v>650</v>
       </c>
       <c r="D541">
         <v>10.9</v>
@@ -18731,7 +18731,7 @@
         <v>425</v>
       </c>
       <c r="H541" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K541" t="s">
         <v>418</v>
@@ -18739,10 +18739,10 @@
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B542" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D542">
         <v>10.9</v>
@@ -18757,7 +18757,7 @@
         <v>425</v>
       </c>
       <c r="H542" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K542" t="s">
         <v>418</v>
@@ -18765,10 +18765,10 @@
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B543" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D543">
         <v>15.2</v>
@@ -18783,7 +18783,7 @@
         <v>425</v>
       </c>
       <c r="H543" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K543" t="s">
         <v>418</v>
@@ -18791,10 +18791,10 @@
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B544" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D544">
         <v>10.8</v>
@@ -18809,7 +18809,7 @@
         <v>425</v>
       </c>
       <c r="H544" t="s">
-        <v>446</v>
+        <v>653</v>
       </c>
       <c r="K544" t="s">
         <v>418</v>
@@ -18821,6 +18821,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="866fd922-7b23-4716-93c2-487563398d18" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010076C38436C713A84BB4AC5F3845060BA5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f8834df46ddabc569667da254ef69d9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="866fd922-7b23-4716-93c2-487563398d18" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cdc573d73b1650fc03355cf1837b4f5" ns3:_="">
     <xsd:import namespace="866fd922-7b23-4716-93c2-487563398d18"/>
@@ -19008,14 +19016,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="866fd922-7b23-4716-93c2-487563398d18" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -19026,6 +19026,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6105A6FC-C584-4E3C-B805-331408F866B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="866fd922-7b23-4716-93c2-487563398d18"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B0411CD-DCB4-4DCB-93C6-27E33BC9B163}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19043,22 +19059,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6105A6FC-C584-4E3C-B805-331408F866B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="866fd922-7b23-4716-93c2-487563398d18"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{281BBDB7-BFCC-4673-8F3B-8980A6C72910}">
   <ds:schemaRefs>

--- a/officialtreedatabase_NFC.xlsx
+++ b/officialtreedatabase_NFC.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livesalemstate-my.sharepoint.com/personal/s0422087_salemstate_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{FA046AD5-917E-4A35-B422-ABFFB660B64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB720A32-ECDD-4BF6-A737-3920FFBD2F0C}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{FA046AD5-917E-4A35-B422-ABFFB660B64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9A3BAE-95AC-4D00-819F-8522201ABC8F}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="13440" xr2:uid="{C06BAD32-CBF9-4080-B573-E5CEA293F44F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="18570" xr2:uid="{C06BAD32-CBF9-4080-B573-E5CEA293F44F}"/>
   </bookViews>
   <sheets>
     <sheet name="officialtreedatabase_NFC" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1292,9 +1292,6 @@
     <t>Jeremiah</t>
   </si>
   <si>
-    <t>south campus</t>
-  </si>
-  <si>
     <t>AH2</t>
   </si>
   <si>
@@ -1998,6 +1995,9 @@
   </si>
   <si>
     <t>amanda &amp; mia</t>
+  </si>
+  <si>
+    <t>central  campus</t>
   </si>
 </sst>
 </file>
@@ -2051,6 +2051,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14054,12 +14058,12 @@
         <v>417</v>
       </c>
       <c r="K361" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B362" t="s">
         <v>233</v>
@@ -14080,12 +14084,12 @@
         <v>417</v>
       </c>
       <c r="K362" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B363" t="s">
         <v>233</v>
@@ -14106,12 +14110,12 @@
         <v>417</v>
       </c>
       <c r="K363" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B364" t="s">
         <v>233</v>
@@ -14132,12 +14136,12 @@
         <v>417</v>
       </c>
       <c r="K364" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B365" t="s">
         <v>233</v>
@@ -14158,15 +14162,15 @@
         <v>417</v>
       </c>
       <c r="K365" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>422</v>
+      </c>
+      <c r="B366" t="s">
         <v>423</v>
-      </c>
-      <c r="B366" t="s">
-        <v>424</v>
       </c>
       <c r="D366">
         <v>8.6</v>
@@ -14178,21 +14182,21 @@
         <v>1</v>
       </c>
       <c r="G366" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H366" t="s">
         <v>417</v>
       </c>
       <c r="K366" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B367" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D367">
         <v>8.6999999999999993</v>
@@ -14204,21 +14208,21 @@
         <v>1</v>
       </c>
       <c r="G367" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H367" t="s">
         <v>417</v>
       </c>
       <c r="K367" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B368" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D368">
         <v>8.6</v>
@@ -14230,21 +14234,21 @@
         <v>1</v>
       </c>
       <c r="G368" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H368" t="s">
         <v>417</v>
       </c>
       <c r="K368" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="369" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B369" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D369">
         <v>8.6</v>
@@ -14262,15 +14266,15 @@
         <v>417</v>
       </c>
       <c r="K369" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B370" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D370">
         <v>8.6</v>
@@ -14282,21 +14286,21 @@
         <v>1</v>
       </c>
       <c r="G370" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H370" t="s">
         <v>417</v>
       </c>
       <c r="K370" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
+        <v>429</v>
+      </c>
+      <c r="B371" t="s">
         <v>430</v>
-      </c>
-      <c r="B371" t="s">
-        <v>431</v>
       </c>
       <c r="D371">
         <v>9.75</v>
@@ -14308,21 +14312,21 @@
         <v>2</v>
       </c>
       <c r="G371" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H371" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K371" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B372" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D372">
         <v>9.1</v>
@@ -14334,21 +14338,21 @@
         <v>2</v>
       </c>
       <c r="G372" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H372" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K372" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B373" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D373">
         <v>9.1999999999999993</v>
@@ -14360,21 +14364,21 @@
         <v>2</v>
       </c>
       <c r="G373" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H373" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K373" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B374" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D374">
         <v>8.5</v>
@@ -14386,21 +14390,21 @@
         <v>2</v>
       </c>
       <c r="G374" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H374" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K374" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B375" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D375">
         <v>9.3000000000000007</v>
@@ -14412,18 +14416,18 @@
         <v>2</v>
       </c>
       <c r="G375" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H375" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K375" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B376" t="s">
         <v>233</v>
@@ -14441,15 +14445,15 @@
         <v>416</v>
       </c>
       <c r="H376" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K376" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B377" t="s">
         <v>233</v>
@@ -14464,18 +14468,18 @@
         <v>1</v>
       </c>
       <c r="G377" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H377" t="s">
         <v>417</v>
       </c>
       <c r="K377" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B378" t="s">
         <v>233</v>
@@ -14490,18 +14494,18 @@
         <v>1</v>
       </c>
       <c r="G378" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H378" t="s">
         <v>417</v>
       </c>
       <c r="K378" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B379" t="s">
         <v>233</v>
@@ -14516,18 +14520,18 @@
         <v>1</v>
       </c>
       <c r="G379" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H379" t="s">
         <v>417</v>
       </c>
       <c r="K379" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B380" t="s">
         <v>233</v>
@@ -14542,21 +14546,21 @@
         <v>1</v>
       </c>
       <c r="G380" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H380" t="s">
         <v>417</v>
       </c>
       <c r="K380" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>441</v>
+      </c>
+      <c r="B381" t="s">
         <v>442</v>
-      </c>
-      <c r="B381" t="s">
-        <v>443</v>
       </c>
       <c r="D381">
         <v>11.8</v>
@@ -14568,21 +14572,21 @@
         <v>1</v>
       </c>
       <c r="G381" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H381" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K381" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B382" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D382">
         <v>9.5</v>
@@ -14594,21 +14598,21 @@
         <v>1</v>
       </c>
       <c r="G382" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H382" t="s">
+        <v>652</v>
+      </c>
+      <c r="K382" t="s">
         <v>653</v>
-      </c>
-      <c r="K382" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B383" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D383">
         <v>10.8</v>
@@ -14620,21 +14624,21 @@
         <v>1</v>
       </c>
       <c r="G383" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H383" t="s">
+        <v>652</v>
+      </c>
+      <c r="K383" t="s">
         <v>653</v>
-      </c>
-      <c r="K383" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B384" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D384">
         <v>12.7</v>
@@ -14646,21 +14650,21 @@
         <v>1</v>
       </c>
       <c r="G384" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H384" t="s">
+        <v>652</v>
+      </c>
+      <c r="K384" t="s">
         <v>653</v>
-      </c>
-      <c r="K384" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="385" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B385" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D385">
         <v>11.3</v>
@@ -14672,21 +14676,21 @@
         <v>1</v>
       </c>
       <c r="G385" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H385" t="s">
+        <v>652</v>
+      </c>
+      <c r="K385" t="s">
         <v>653</v>
-      </c>
-      <c r="K385" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B386" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D386">
         <v>10.8</v>
@@ -14698,21 +14702,21 @@
         <v>1</v>
       </c>
       <c r="G386" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H386" t="s">
+        <v>652</v>
+      </c>
+      <c r="K386" t="s">
         <v>653</v>
-      </c>
-      <c r="K386" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="387" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B387" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D387">
         <v>9.1999999999999993</v>
@@ -14724,21 +14728,21 @@
         <v>1</v>
       </c>
       <c r="G387" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H387" t="s">
+        <v>652</v>
+      </c>
+      <c r="K387" t="s">
         <v>653</v>
-      </c>
-      <c r="K387" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="388" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B388" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D388">
         <v>12.4</v>
@@ -14750,21 +14754,21 @@
         <v>1</v>
       </c>
       <c r="G388" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H388" t="s">
+        <v>652</v>
+      </c>
+      <c r="K388" t="s">
         <v>653</v>
-      </c>
-      <c r="K388" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B389" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D389">
         <v>10.9</v>
@@ -14776,21 +14780,21 @@
         <v>1</v>
       </c>
       <c r="G389" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H389" t="s">
+        <v>652</v>
+      </c>
+      <c r="K389" t="s">
         <v>653</v>
-      </c>
-      <c r="K389" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
+        <v>452</v>
+      </c>
+      <c r="B390" t="s">
         <v>453</v>
-      </c>
-      <c r="B390" t="s">
-        <v>454</v>
       </c>
       <c r="D390">
         <v>9.6</v>
@@ -14802,21 +14806,21 @@
         <v>1</v>
       </c>
       <c r="G390" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H390" t="s">
+        <v>652</v>
+      </c>
+      <c r="K390" t="s">
         <v>653</v>
-      </c>
-      <c r="K390" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B391" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D391">
         <v>7.9</v>
@@ -14828,21 +14832,21 @@
         <v>1</v>
       </c>
       <c r="G391" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H391" t="s">
+        <v>652</v>
+      </c>
+      <c r="K391" t="s">
         <v>653</v>
-      </c>
-      <c r="K391" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B392" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D392">
         <v>9.6</v>
@@ -14854,21 +14858,21 @@
         <v>1</v>
       </c>
       <c r="G392" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H392" t="s">
+        <v>652</v>
+      </c>
+      <c r="K392" t="s">
         <v>653</v>
-      </c>
-      <c r="K392" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B393" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D393">
         <v>5.9</v>
@@ -14880,21 +14884,21 @@
         <v>2</v>
       </c>
       <c r="G393" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H393" t="s">
+        <v>652</v>
+      </c>
+      <c r="K393" t="s">
         <v>653</v>
-      </c>
-      <c r="K393" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B394" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D394">
         <v>5.8</v>
@@ -14906,21 +14910,21 @@
         <v>2</v>
       </c>
       <c r="G394" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H394" t="s">
+        <v>652</v>
+      </c>
+      <c r="K394" t="s">
         <v>653</v>
-      </c>
-      <c r="K394" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B395" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D395">
         <v>8.1</v>
@@ -14932,21 +14936,21 @@
         <v>2</v>
       </c>
       <c r="G395" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H395" t="s">
+        <v>652</v>
+      </c>
+      <c r="K395" t="s">
         <v>653</v>
-      </c>
-      <c r="K395" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B396" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D396">
         <v>7.8</v>
@@ -14958,21 +14962,21 @@
         <v>2</v>
       </c>
       <c r="G396" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H396" t="s">
+        <v>652</v>
+      </c>
+      <c r="K396" t="s">
         <v>653</v>
-      </c>
-      <c r="K396" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B397" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D397">
         <v>9</v>
@@ -14984,21 +14988,21 @@
         <v>2</v>
       </c>
       <c r="G397" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H397" t="s">
+        <v>652</v>
+      </c>
+      <c r="K397" t="s">
         <v>653</v>
-      </c>
-      <c r="K397" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B398" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D398">
         <v>6.4</v>
@@ -15010,21 +15014,21 @@
         <v>2</v>
       </c>
       <c r="G398" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H398" t="s">
+        <v>652</v>
+      </c>
+      <c r="K398" t="s">
         <v>653</v>
-      </c>
-      <c r="K398" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B399" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D399">
         <v>5.2</v>
@@ -15036,21 +15040,21 @@
         <v>2</v>
       </c>
       <c r="G399" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H399" t="s">
+        <v>652</v>
+      </c>
+      <c r="K399" t="s">
         <v>653</v>
-      </c>
-      <c r="K399" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
+        <v>463</v>
+      </c>
+      <c r="B400" t="s">
         <v>464</v>
-      </c>
-      <c r="B400" t="s">
-        <v>465</v>
       </c>
       <c r="D400">
         <v>11.2</v>
@@ -15062,21 +15066,21 @@
         <v>1</v>
       </c>
       <c r="G400" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H400" t="s">
+        <v>652</v>
+      </c>
+      <c r="K400" t="s">
         <v>653</v>
-      </c>
-      <c r="K400" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B401" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D401">
         <v>8.9</v>
@@ -15088,21 +15092,21 @@
         <v>2</v>
       </c>
       <c r="G401" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H401" t="s">
+        <v>652</v>
+      </c>
+      <c r="K401" t="s">
         <v>653</v>
-      </c>
-      <c r="K401" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B402" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D402">
         <v>5.9</v>
@@ -15114,21 +15118,21 @@
         <v>2</v>
       </c>
       <c r="G402" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H402" t="s">
+        <v>652</v>
+      </c>
+      <c r="K402" t="s">
         <v>653</v>
-      </c>
-      <c r="K402" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B403" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D403">
         <v>8</v>
@@ -15140,21 +15144,21 @@
         <v>2</v>
       </c>
       <c r="G403" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H403" t="s">
+        <v>652</v>
+      </c>
+      <c r="K403" t="s">
         <v>653</v>
-      </c>
-      <c r="K403" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B404" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D404">
         <v>5.6</v>
@@ -15166,21 +15170,21 @@
         <v>2</v>
       </c>
       <c r="G404" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H404" t="s">
+        <v>652</v>
+      </c>
+      <c r="K404" t="s">
         <v>653</v>
-      </c>
-      <c r="K404" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B405" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D405">
         <v>5.3</v>
@@ -15192,21 +15196,21 @@
         <v>2</v>
       </c>
       <c r="G405" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H405" t="s">
+        <v>652</v>
+      </c>
+      <c r="K405" t="s">
         <v>653</v>
-      </c>
-      <c r="K405" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B406" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D406">
         <v>6.3</v>
@@ -15218,21 +15222,21 @@
         <v>2</v>
       </c>
       <c r="G406" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H406" t="s">
+        <v>652</v>
+      </c>
+      <c r="K406" t="s">
         <v>653</v>
-      </c>
-      <c r="K406" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="407" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B407" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D407">
         <v>5.7</v>
@@ -15244,18 +15248,18 @@
         <v>2</v>
       </c>
       <c r="G407" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H407" t="s">
+        <v>652</v>
+      </c>
+      <c r="K407" t="s">
         <v>653</v>
-      </c>
-      <c r="K407" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B408" t="s">
         <v>99</v>
@@ -15270,21 +15274,21 @@
         <v>1</v>
       </c>
       <c r="G408" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H408" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K408" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B409" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D409">
         <v>9</v>
@@ -15299,18 +15303,18 @@
         <v>416</v>
       </c>
       <c r="H409" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K409" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B410" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D410">
         <v>9.4499999999999993</v>
@@ -15325,18 +15329,18 @@
         <v>13</v>
       </c>
       <c r="H410" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K410" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B411" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D411">
         <v>7.4</v>
@@ -15351,18 +15355,18 @@
         <v>13</v>
       </c>
       <c r="H411" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K411" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B412" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D412">
         <v>7.13</v>
@@ -15377,18 +15381,18 @@
         <v>13</v>
       </c>
       <c r="H412" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K412" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B413" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D413">
         <v>12.4</v>
@@ -15400,21 +15404,21 @@
         <v>1</v>
       </c>
       <c r="G413" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H413" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="K413" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B414" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D414">
         <v>7.28</v>
@@ -15429,18 +15433,18 @@
         <v>13</v>
       </c>
       <c r="H414" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K414" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B415" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D415">
         <v>6.9</v>
@@ -15455,18 +15459,18 @@
         <v>13</v>
       </c>
       <c r="H415" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K415" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B416" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D416">
         <v>6.91</v>
@@ -15481,18 +15485,18 @@
         <v>13</v>
       </c>
       <c r="H416" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K416" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
+        <v>484</v>
+      </c>
+      <c r="B417" t="s">
         <v>485</v>
-      </c>
-      <c r="B417" t="s">
-        <v>486</v>
       </c>
       <c r="D417">
         <v>3.1</v>
@@ -15507,18 +15511,18 @@
         <v>31</v>
       </c>
       <c r="H417" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K417" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>486</v>
+      </c>
+      <c r="B418" t="s">
         <v>487</v>
-      </c>
-      <c r="B418" t="s">
-        <v>488</v>
       </c>
       <c r="D418">
         <v>5.19</v>
@@ -15533,18 +15537,18 @@
         <v>13</v>
       </c>
       <c r="H418" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K418" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B419" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D419">
         <v>3.12</v>
@@ -15559,18 +15563,18 @@
         <v>13</v>
       </c>
       <c r="H419" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K419" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B420" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D420">
         <v>6.1</v>
@@ -15585,18 +15589,18 @@
         <v>13</v>
       </c>
       <c r="H420" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K420" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
+        <v>490</v>
+      </c>
+      <c r="B421" t="s">
         <v>491</v>
-      </c>
-      <c r="B421" t="s">
-        <v>492</v>
       </c>
       <c r="D421">
         <v>3.92</v>
@@ -15611,18 +15615,18 @@
         <v>13</v>
       </c>
       <c r="H421" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="K421" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
+        <v>492</v>
+      </c>
+      <c r="B422" t="s">
         <v>493</v>
-      </c>
-      <c r="B422" t="s">
-        <v>494</v>
       </c>
       <c r="D422">
         <v>42.33</v>
@@ -15637,18 +15641,18 @@
         <v>13</v>
       </c>
       <c r="H422" t="s">
+        <v>652</v>
+      </c>
+      <c r="K422" t="s">
         <v>653</v>
-      </c>
-      <c r="K422" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
+        <v>494</v>
+      </c>
+      <c r="B423" t="s">
         <v>495</v>
-      </c>
-      <c r="B423" t="s">
-        <v>496</v>
       </c>
       <c r="D423">
         <v>4.0999999999999996</v>
@@ -15663,18 +15667,18 @@
         <v>31</v>
       </c>
       <c r="H423" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K423" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B424" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D424">
         <v>4.0999999999999996</v>
@@ -15689,18 +15693,18 @@
         <v>31</v>
       </c>
       <c r="H424" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K424" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B425" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D425">
         <v>3.6</v>
@@ -15715,15 +15719,15 @@
         <v>31</v>
       </c>
       <c r="H425" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K425" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B426" t="s">
         <v>99</v>
@@ -15738,18 +15742,18 @@
         <v>1</v>
       </c>
       <c r="G426" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H426" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K426" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="427" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B427" t="s">
         <v>99</v>
@@ -15764,18 +15768,18 @@
         <v>1</v>
       </c>
       <c r="G427" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H427" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K427" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B428" t="s">
         <v>99</v>
@@ -15790,21 +15794,21 @@
         <v>1</v>
       </c>
       <c r="G428" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H428" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K428" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B429" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D429">
         <v>4.4000000000000004</v>
@@ -15819,18 +15823,18 @@
         <v>13</v>
       </c>
       <c r="H429" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K429" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B430" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D430">
         <v>3.4</v>
@@ -15845,18 +15849,18 @@
         <v>13</v>
       </c>
       <c r="H430" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K430" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B431" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D431">
         <v>4.3</v>
@@ -15871,15 +15875,15 @@
         <v>13</v>
       </c>
       <c r="H431" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K431" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B432" t="s">
         <v>233</v>
@@ -15897,15 +15901,15 @@
         <v>31</v>
       </c>
       <c r="H432" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K432" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B433" t="s">
         <v>233</v>
@@ -15923,18 +15927,18 @@
         <v>31</v>
       </c>
       <c r="H433" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="K433" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
+        <v>509</v>
+      </c>
+      <c r="B434" t="s">
         <v>510</v>
-      </c>
-      <c r="B434" t="s">
-        <v>511</v>
       </c>
       <c r="D434">
         <v>2.1</v>
@@ -15949,18 +15953,18 @@
         <v>28</v>
       </c>
       <c r="H434" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K434" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B435" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D435">
         <v>4.2</v>
@@ -15972,21 +15976,21 @@
         <v>1</v>
       </c>
       <c r="G435" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H435" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K435" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B436" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D436">
         <v>2.5</v>
@@ -16001,18 +16005,18 @@
         <v>13</v>
       </c>
       <c r="H436" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K436" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B437" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D437">
         <v>5.8</v>
@@ -16024,21 +16028,21 @@
         <v>1</v>
       </c>
       <c r="G437" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H437" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K437" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B438" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D438">
         <v>5.0999999999999996</v>
@@ -16050,18 +16054,18 @@
         <v>1</v>
       </c>
       <c r="G438" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H438" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K438" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B439" t="s">
         <v>99</v>
@@ -16076,18 +16080,18 @@
         <v>1</v>
       </c>
       <c r="G439" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H439" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K439" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B440" t="s">
         <v>99</v>
@@ -16102,18 +16106,18 @@
         <v>1</v>
       </c>
       <c r="G440" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H440" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K440" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B441" t="s">
         <v>99</v>
@@ -16128,18 +16132,18 @@
         <v>1</v>
       </c>
       <c r="G441" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H441" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K441" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B442" t="s">
         <v>99</v>
@@ -16154,18 +16158,18 @@
         <v>1</v>
       </c>
       <c r="G442" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H442" t="s">
+        <v>652</v>
+      </c>
+      <c r="K442" t="s">
         <v>653</v>
-      </c>
-      <c r="K442" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B443" t="s">
         <v>99</v>
@@ -16180,18 +16184,18 @@
         <v>1</v>
       </c>
       <c r="G443" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H443" t="s">
+        <v>652</v>
+      </c>
+      <c r="K443" t="s">
         <v>653</v>
-      </c>
-      <c r="K443" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B444" t="s">
         <v>99</v>
@@ -16206,18 +16210,18 @@
         <v>1</v>
       </c>
       <c r="G444" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H444" t="s">
+        <v>652</v>
+      </c>
+      <c r="K444" t="s">
         <v>653</v>
-      </c>
-      <c r="K444" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B445" t="s">
         <v>99</v>
@@ -16232,18 +16236,18 @@
         <v>1</v>
       </c>
       <c r="G445" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H445" t="s">
+        <v>652</v>
+      </c>
+      <c r="K445" t="s">
         <v>653</v>
-      </c>
-      <c r="K445" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B446" t="s">
         <v>99</v>
@@ -16258,21 +16262,21 @@
         <v>1</v>
       </c>
       <c r="G446" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H446" t="s">
+        <v>652</v>
+      </c>
+      <c r="K446" t="s">
         <v>653</v>
-      </c>
-      <c r="K446" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B447" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D447">
         <v>3</v>
@@ -16284,21 +16288,21 @@
         <v>1</v>
       </c>
       <c r="G447" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H447" t="s">
+        <v>652</v>
+      </c>
+      <c r="K447" t="s">
         <v>653</v>
-      </c>
-      <c r="K447" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
+        <v>525</v>
+      </c>
+      <c r="B448" t="s">
         <v>526</v>
-      </c>
-      <c r="B448" t="s">
-        <v>527</v>
       </c>
       <c r="D448">
         <v>3.9</v>
@@ -16313,18 +16317,18 @@
         <v>416</v>
       </c>
       <c r="H448" t="s">
+        <v>652</v>
+      </c>
+      <c r="K448" t="s">
         <v>653</v>
-      </c>
-      <c r="K448" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B449" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D449">
         <v>4.5999999999999996</v>
@@ -16336,21 +16340,21 @@
         <v>1</v>
       </c>
       <c r="G449" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H449" t="s">
+        <v>652</v>
+      </c>
+      <c r="K449" t="s">
         <v>653</v>
-      </c>
-      <c r="K449" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B450" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D450">
         <v>4.7</v>
@@ -16362,21 +16366,21 @@
         <v>1</v>
       </c>
       <c r="G450" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H450" t="s">
+        <v>652</v>
+      </c>
+      <c r="K450" t="s">
         <v>653</v>
-      </c>
-      <c r="K450" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B451" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D451">
         <v>5.7</v>
@@ -16388,21 +16392,21 @@
         <v>1</v>
       </c>
       <c r="G451" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H451" t="s">
+        <v>652</v>
+      </c>
+      <c r="K451" t="s">
         <v>653</v>
-      </c>
-      <c r="K451" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
+        <v>530</v>
+      </c>
+      <c r="B452" t="s">
         <v>531</v>
-      </c>
-      <c r="B452" t="s">
-        <v>532</v>
       </c>
       <c r="D452">
         <v>4.2</v>
@@ -16414,21 +16418,21 @@
         <v>1</v>
       </c>
       <c r="G452" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H452" t="s">
+        <v>652</v>
+      </c>
+      <c r="K452" t="s">
         <v>653</v>
-      </c>
-      <c r="K452" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B453" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D453">
         <v>5.7</v>
@@ -16443,18 +16447,18 @@
         <v>13</v>
       </c>
       <c r="H453" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K453" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B454" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D454">
         <v>5.7</v>
@@ -16469,18 +16473,18 @@
         <v>13</v>
       </c>
       <c r="H454" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K454" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B455" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D455">
         <v>5.7</v>
@@ -16495,18 +16499,18 @@
         <v>13</v>
       </c>
       <c r="H455" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K455" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B456" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D456">
         <v>5.8</v>
@@ -16521,18 +16525,18 @@
         <v>13</v>
       </c>
       <c r="H456" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K456" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B457" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D457">
         <v>2.1</v>
@@ -16547,18 +16551,18 @@
         <v>13</v>
       </c>
       <c r="H457" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K457" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B458" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D458">
         <v>0</v>
@@ -16573,18 +16577,18 @@
         <v>13</v>
       </c>
       <c r="H458" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K458" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>539</v>
+      </c>
+      <c r="B459" t="s">
         <v>540</v>
-      </c>
-      <c r="B459" t="s">
-        <v>541</v>
       </c>
       <c r="D459">
         <v>8.3000000000000007</v>
@@ -16599,18 +16603,18 @@
         <v>13</v>
       </c>
       <c r="H459" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K459" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B460" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D460">
         <v>7</v>
@@ -16622,21 +16626,21 @@
         <v>3</v>
       </c>
       <c r="G460" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H460" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K460" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
+        <v>543</v>
+      </c>
+      <c r="B461" t="s">
         <v>544</v>
-      </c>
-      <c r="B461" t="s">
-        <v>545</v>
       </c>
       <c r="D461">
         <v>7.3</v>
@@ -16651,18 +16655,18 @@
         <v>13</v>
       </c>
       <c r="H461" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K461" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B462" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D462">
         <v>6.7</v>
@@ -16674,21 +16678,21 @@
         <v>3</v>
       </c>
       <c r="G462" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H462" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K462" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B463" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D463">
         <v>8.3000000000000007</v>
@@ -16700,21 +16704,21 @@
         <v>3</v>
       </c>
       <c r="G463" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H463" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K463" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B464" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D464">
         <v>5.5</v>
@@ -16726,21 +16730,21 @@
         <v>1</v>
       </c>
       <c r="G464" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H464" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K464" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B465" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D465">
         <v>6.05</v>
@@ -16752,21 +16756,21 @@
         <v>1</v>
       </c>
       <c r="G465" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H465" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K465" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
+        <v>550</v>
+      </c>
+      <c r="B466" t="s">
         <v>551</v>
-      </c>
-      <c r="B466" t="s">
-        <v>552</v>
       </c>
       <c r="D466">
         <v>4.4000000000000004</v>
@@ -16781,18 +16785,18 @@
         <v>13</v>
       </c>
       <c r="H466" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K466" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B467" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D467">
         <v>6.4</v>
@@ -16807,18 +16811,18 @@
         <v>13</v>
       </c>
       <c r="H467" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K467" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B468" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D468">
         <v>7.3</v>
@@ -16833,18 +16837,18 @@
         <v>31</v>
       </c>
       <c r="H468" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K468" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B469" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D469">
         <v>6</v>
@@ -16859,18 +16863,18 @@
         <v>416</v>
       </c>
       <c r="H469" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K469" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B470" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D470">
         <v>4.9000000000000004</v>
@@ -16882,21 +16886,21 @@
         <v>1</v>
       </c>
       <c r="G470" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H470" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K470" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B471" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D471">
         <v>4.7</v>
@@ -16908,21 +16912,21 @@
         <v>1</v>
       </c>
       <c r="G471" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H471" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K471" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B472" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D472">
         <v>4.5</v>
@@ -16934,21 +16938,21 @@
         <v>1</v>
       </c>
       <c r="G472" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H472" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K472" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B473" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D473">
         <v>5.7</v>
@@ -16963,18 +16967,18 @@
         <v>31</v>
       </c>
       <c r="H473" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K473" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B474" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D474">
         <v>8</v>
@@ -16989,18 +16993,18 @@
         <v>31</v>
       </c>
       <c r="H474" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K474" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B475" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D475">
         <v>5.3</v>
@@ -17012,21 +17016,21 @@
         <v>1</v>
       </c>
       <c r="G475" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H475" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K475" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B476" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D476">
         <v>4.5</v>
@@ -17041,18 +17045,18 @@
         <v>416</v>
       </c>
       <c r="H476" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K476" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B477" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D477">
         <v>4.0999999999999996</v>
@@ -17064,21 +17068,21 @@
         <v>1</v>
       </c>
       <c r="G477" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H477" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K477" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B478" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D478">
         <v>4.0999999999999996</v>
@@ -17090,21 +17094,21 @@
         <v>1</v>
       </c>
       <c r="G478" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H478" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K478" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="479" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B479" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D479">
         <v>3.9</v>
@@ -17116,21 +17120,21 @@
         <v>1</v>
       </c>
       <c r="G479" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H479" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K479" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B480" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D480">
         <v>6.8</v>
@@ -17142,21 +17146,21 @@
         <v>1</v>
       </c>
       <c r="G480" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H480" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K480" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B481" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D481">
         <v>6.8</v>
@@ -17168,21 +17172,21 @@
         <v>1</v>
       </c>
       <c r="G481" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H481" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K481" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B482" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D482">
         <v>5.2</v>
@@ -17194,21 +17198,21 @@
         <v>1</v>
       </c>
       <c r="G482" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H482" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K482" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="483" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B483" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D483">
         <v>5.7</v>
@@ -17220,21 +17224,21 @@
         <v>1</v>
       </c>
       <c r="G483" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H483" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="K483" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B484" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D484">
         <v>4.9000000000000004</v>
@@ -17249,18 +17253,18 @@
         <v>416</v>
       </c>
       <c r="H484" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K484" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B485" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D485">
         <v>4.0999999999999996</v>
@@ -17275,18 +17279,18 @@
         <v>416</v>
       </c>
       <c r="H485" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K485" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B486" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D486">
         <v>5.9</v>
@@ -17301,18 +17305,18 @@
         <v>416</v>
       </c>
       <c r="H486" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K486" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B487" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D487">
         <v>6.4</v>
@@ -17327,18 +17331,18 @@
         <v>416</v>
       </c>
       <c r="H487" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K487" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
+        <v>576</v>
+      </c>
+      <c r="B488" t="s">
         <v>577</v>
-      </c>
-      <c r="B488" t="s">
-        <v>578</v>
       </c>
       <c r="D488">
         <v>4.7</v>
@@ -17353,18 +17357,18 @@
         <v>416</v>
       </c>
       <c r="H488" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K488" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="489" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B489" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D489">
         <v>4.8</v>
@@ -17379,18 +17383,18 @@
         <v>416</v>
       </c>
       <c r="H489" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K489" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B490" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D490">
         <v>4.5999999999999996</v>
@@ -17405,18 +17409,18 @@
         <v>13</v>
       </c>
       <c r="H490" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K490" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B491" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D491">
         <v>5.6</v>
@@ -17431,18 +17435,18 @@
         <v>416</v>
       </c>
       <c r="H491" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K491" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B492" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D492">
         <v>5.9</v>
@@ -17457,18 +17461,18 @@
         <v>416</v>
       </c>
       <c r="H492" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K492" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="493" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B493" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D493">
         <v>4.5999999999999996</v>
@@ -17483,18 +17487,18 @@
         <v>416</v>
       </c>
       <c r="H493" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="K493" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
+        <v>583</v>
+      </c>
+      <c r="B494" t="s">
         <v>584</v>
-      </c>
-      <c r="B494" t="s">
-        <v>585</v>
       </c>
       <c r="D494">
         <v>6.7</v>
@@ -17509,18 +17513,18 @@
         <v>13</v>
       </c>
       <c r="H494" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K494" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="495" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B495" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D495">
         <v>5.4</v>
@@ -17532,21 +17536,21 @@
         <v>1</v>
       </c>
       <c r="G495" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H495" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K495" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="496" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B496" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D496">
         <v>5.8</v>
@@ -17558,21 +17562,21 @@
         <v>1</v>
       </c>
       <c r="G496" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H496" t="s">
+        <v>652</v>
+      </c>
+      <c r="K496" t="s">
         <v>653</v>
-      </c>
-      <c r="K496" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="497" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B497" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D497">
         <v>6.8</v>
@@ -17584,21 +17588,21 @@
         <v>1</v>
       </c>
       <c r="G497" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H497" t="s">
+        <v>652</v>
+      </c>
+      <c r="K497" t="s">
         <v>653</v>
-      </c>
-      <c r="K497" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="498" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B498" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D498">
         <v>7.9</v>
@@ -17613,18 +17617,18 @@
         <v>13</v>
       </c>
       <c r="H498" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="K498" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="499" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B499" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D499">
         <v>1.2</v>
@@ -17636,21 +17640,21 @@
         <v>1</v>
       </c>
       <c r="G499" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H499" t="s">
+        <v>652</v>
+      </c>
+      <c r="K499" t="s">
         <v>653</v>
-      </c>
-      <c r="K499" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="500" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B500" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D500">
         <v>7.6</v>
@@ -17662,21 +17666,21 @@
         <v>1</v>
       </c>
       <c r="G500" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H500" t="s">
+        <v>652</v>
+      </c>
+      <c r="K500" t="s">
         <v>653</v>
-      </c>
-      <c r="K500" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="501" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B501" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D501">
         <v>4.0999999999999996</v>
@@ -17688,21 +17692,21 @@
         <v>0</v>
       </c>
       <c r="G501" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H501" t="s">
+        <v>652</v>
+      </c>
+      <c r="K501" t="s">
         <v>653</v>
-      </c>
-      <c r="K501" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="502" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B502" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D502">
         <v>6.3</v>
@@ -17714,21 +17718,21 @@
         <v>1</v>
       </c>
       <c r="G502" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H502" t="s">
+        <v>652</v>
+      </c>
+      <c r="K502" t="s">
         <v>653</v>
-      </c>
-      <c r="K502" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B503" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D503">
         <v>7.6</v>
@@ -17740,21 +17744,21 @@
         <v>1</v>
       </c>
       <c r="G503" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H503" t="s">
+        <v>652</v>
+      </c>
+      <c r="K503" t="s">
         <v>653</v>
-      </c>
-      <c r="K503" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B504" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D504">
         <v>7.1</v>
@@ -17766,21 +17770,21 @@
         <v>1</v>
       </c>
       <c r="G504" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H504" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K504" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B505" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D505">
         <v>4.0999999999999996</v>
@@ -17795,18 +17799,18 @@
         <v>416</v>
       </c>
       <c r="H505" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K505" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B506" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D506">
         <v>4.3</v>
@@ -17818,21 +17822,21 @@
         <v>1</v>
       </c>
       <c r="G506" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H506" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K506" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B507" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D507">
         <v>0</v>
@@ -17847,18 +17851,18 @@
         <v>416</v>
       </c>
       <c r="H507" t="s">
+        <v>652</v>
+      </c>
+      <c r="K507" t="s">
         <v>653</v>
-      </c>
-      <c r="K507" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B508" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D508">
         <v>5.8</v>
@@ -17870,21 +17874,21 @@
         <v>2</v>
       </c>
       <c r="G508" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H508" t="s">
+        <v>652</v>
+      </c>
+      <c r="K508" t="s">
         <v>653</v>
-      </c>
-      <c r="K508" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B509" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D509">
         <v>3.5</v>
@@ -17896,21 +17900,21 @@
         <v>1</v>
       </c>
       <c r="G509" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H509" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K509" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="510" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B510" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D510">
         <v>7.1</v>
@@ -17922,21 +17926,21 @@
         <v>2</v>
       </c>
       <c r="G510" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H510" t="s">
+        <v>652</v>
+      </c>
+      <c r="K510" t="s">
         <v>653</v>
-      </c>
-      <c r="K510" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
+        <v>606</v>
+      </c>
+      <c r="B511" t="s">
         <v>607</v>
-      </c>
-      <c r="B511" t="s">
-        <v>608</v>
       </c>
       <c r="D511">
         <v>2.38</v>
@@ -17951,18 +17955,18 @@
         <v>416</v>
       </c>
       <c r="H511" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K511" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B512" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D512">
         <v>2.38</v>
@@ -17977,18 +17981,18 @@
         <v>13</v>
       </c>
       <c r="H512" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K512" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="513" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B513" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D513">
         <v>2.38</v>
@@ -18003,18 +18007,18 @@
         <v>31</v>
       </c>
       <c r="H513" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K513" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B514" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D514">
         <v>2.38</v>
@@ -18029,18 +18033,18 @@
         <v>31</v>
       </c>
       <c r="H514" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K514" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
+        <v>614</v>
+      </c>
+      <c r="B515" t="s">
         <v>615</v>
-      </c>
-      <c r="B515" t="s">
-        <v>616</v>
       </c>
       <c r="D515">
         <v>5.9</v>
@@ -18052,21 +18056,21 @@
         <v>1</v>
       </c>
       <c r="G515" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H515" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K515" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
+        <v>616</v>
+      </c>
+      <c r="B516" t="s">
         <v>617</v>
-      </c>
-      <c r="B516" t="s">
-        <v>618</v>
       </c>
       <c r="D516">
         <v>1.5</v>
@@ -18081,18 +18085,18 @@
         <v>13</v>
       </c>
       <c r="H516" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K516" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B517" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D517">
         <v>2.8</v>
@@ -18107,18 +18111,18 @@
         <v>13</v>
       </c>
       <c r="H517" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K517" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
+        <v>619</v>
+      </c>
+      <c r="B518" t="s">
         <v>620</v>
-      </c>
-      <c r="B518" t="s">
-        <v>621</v>
       </c>
       <c r="D518">
         <v>12.1</v>
@@ -18133,18 +18137,18 @@
         <v>416</v>
       </c>
       <c r="H518" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K518" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B519" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D519">
         <v>3.6</v>
@@ -18159,18 +18163,18 @@
         <v>416</v>
       </c>
       <c r="H519" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K519" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B520" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D520">
         <v>2.5</v>
@@ -18182,21 +18186,21 @@
         <v>1</v>
       </c>
       <c r="G520" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H520" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K520" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
+        <v>623</v>
+      </c>
+      <c r="B521" t="s">
         <v>624</v>
-      </c>
-      <c r="B521" t="s">
-        <v>625</v>
       </c>
       <c r="D521">
         <v>8.6999999999999993</v>
@@ -18211,18 +18215,18 @@
         <v>416</v>
       </c>
       <c r="H521" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K521" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B522" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D522">
         <v>9.5</v>
@@ -18237,18 +18241,18 @@
         <v>416</v>
       </c>
       <c r="H522" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K522" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B523" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D523">
         <v>10.9</v>
@@ -18260,21 +18264,21 @@
         <v>1</v>
       </c>
       <c r="G523" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H523" t="s">
+        <v>652</v>
+      </c>
+      <c r="K523" t="s">
         <v>653</v>
-      </c>
-      <c r="K523" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B524" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D524">
         <v>10.3</v>
@@ -18286,21 +18290,21 @@
         <v>1</v>
       </c>
       <c r="G524" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H524" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K524" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B525" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D525">
         <v>10.199999999999999</v>
@@ -18312,21 +18316,21 @@
         <v>1</v>
       </c>
       <c r="G525" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H525" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K525" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B526" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D526">
         <v>10</v>
@@ -18338,21 +18342,21 @@
         <v>1</v>
       </c>
       <c r="G526" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H526" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K526" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B527" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D527">
         <v>9.5</v>
@@ -18364,21 +18368,21 @@
         <v>1</v>
       </c>
       <c r="G527" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H527" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K527" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B528" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D528">
         <v>11.1</v>
@@ -18390,21 +18394,21 @@
         <v>1</v>
       </c>
       <c r="G528" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H528" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K528" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
+        <v>632</v>
+      </c>
+      <c r="B529" t="s">
         <v>633</v>
-      </c>
-      <c r="B529" t="s">
-        <v>634</v>
       </c>
       <c r="D529">
         <v>11.4</v>
@@ -18419,18 +18423,18 @@
         <v>416</v>
       </c>
       <c r="H529" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K529" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
+        <v>634</v>
+      </c>
+      <c r="B530" t="s">
         <v>635</v>
-      </c>
-      <c r="B530" t="s">
-        <v>636</v>
       </c>
       <c r="D530">
         <v>9.6999999999999993</v>
@@ -18445,18 +18449,18 @@
         <v>416</v>
       </c>
       <c r="H530" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K530" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="531" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B531" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D531">
         <v>11.4</v>
@@ -18468,21 +18472,21 @@
         <v>1</v>
       </c>
       <c r="G531" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H531" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K531" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B532" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D532">
         <v>11.3</v>
@@ -18494,21 +18498,21 @@
         <v>1</v>
       </c>
       <c r="G532" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H532" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K532" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B533" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D533">
         <v>8.6</v>
@@ -18520,21 +18524,21 @@
         <v>1</v>
       </c>
       <c r="G533" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H533" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K533" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B534" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D534">
         <v>7.2</v>
@@ -18546,21 +18550,21 @@
         <v>3</v>
       </c>
       <c r="G534" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H534" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K534" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B535" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D535">
         <v>11.9</v>
@@ -18572,21 +18576,21 @@
         <v>1</v>
       </c>
       <c r="G535" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H535" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="K535" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B536" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D536">
         <v>12</v>
@@ -18601,18 +18605,18 @@
         <v>416</v>
       </c>
       <c r="H536" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K536" t="s">
-        <v>418</v>
+        <v>653</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B537" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D537">
         <v>11.4</v>
@@ -18624,21 +18628,21 @@
         <v>2</v>
       </c>
       <c r="G537" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H537" t="s">
+        <v>652</v>
+      </c>
+      <c r="K537" t="s">
         <v>653</v>
-      </c>
-      <c r="K537" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B538" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D538">
         <v>9.5</v>
@@ -18650,21 +18654,21 @@
         <v>2</v>
       </c>
       <c r="G538" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H538" t="s">
+        <v>652</v>
+      </c>
+      <c r="K538" t="s">
         <v>653</v>
-      </c>
-      <c r="K538" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B539" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D539">
         <v>11.9</v>
@@ -18676,21 +18680,21 @@
         <v>2</v>
       </c>
       <c r="G539" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H539" t="s">
+        <v>652</v>
+      </c>
+      <c r="K539" t="s">
         <v>653</v>
-      </c>
-      <c r="K539" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B540" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D540">
         <v>12.5</v>
@@ -18702,21 +18706,21 @@
         <v>2</v>
       </c>
       <c r="G540" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H540" t="s">
+        <v>652</v>
+      </c>
+      <c r="K540" t="s">
         <v>653</v>
-      </c>
-      <c r="K540" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="541" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
+        <v>647</v>
+      </c>
+      <c r="B541" t="s">
         <v>648</v>
-      </c>
-      <c r="B541" t="s">
-        <v>649</v>
       </c>
       <c r="D541">
         <v>10.9</v>
@@ -18728,21 +18732,21 @@
         <v>1</v>
       </c>
       <c r="G541" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H541" t="s">
+        <v>652</v>
+      </c>
+      <c r="K541" t="s">
         <v>653</v>
-      </c>
-      <c r="K541" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="542" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B542" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D542">
         <v>10.9</v>
@@ -18754,21 +18758,21 @@
         <v>1</v>
       </c>
       <c r="G542" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H542" t="s">
+        <v>652</v>
+      </c>
+      <c r="K542" t="s">
         <v>653</v>
-      </c>
-      <c r="K542" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B543" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D543">
         <v>15.2</v>
@@ -18780,21 +18784,21 @@
         <v>1</v>
       </c>
       <c r="G543" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H543" t="s">
+        <v>652</v>
+      </c>
+      <c r="K543" t="s">
         <v>653</v>
-      </c>
-      <c r="K543" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B544" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D544">
         <v>10.8</v>
@@ -18806,13 +18810,13 @@
         <v>1</v>
       </c>
       <c r="G544" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H544" t="s">
+        <v>652</v>
+      </c>
+      <c r="K544" t="s">
         <v>653</v>
-      </c>
-      <c r="K544" t="s">
-        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -18821,6 +18825,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="866fd922-7b23-4716-93c2-487563398d18" xsi:nil="true"/>
@@ -18828,7 +18841,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010076C38436C713A84BB4AC5F3845060BA5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3f8834df46ddabc569667da254ef69d9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="866fd922-7b23-4716-93c2-487563398d18" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0cdc573d73b1650fc03355cf1837b4f5" ns3:_="">
     <xsd:import namespace="866fd922-7b23-4716-93c2-487563398d18"/>
@@ -19016,16 +19029,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{281BBDB7-BFCC-4673-8F3B-8980A6C72910}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6105A6FC-C584-4E3C-B805-331408F866B8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -19041,7 +19053,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B0411CD-DCB4-4DCB-93C6-27E33BC9B163}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19059,14 +19071,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{281BBDB7-BFCC-4673-8F3B-8980A6C72910}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{70d32b73-b457-49d1-950c-4f78aeffc21b}" enabled="0" method="" siteId="{70d32b73-b457-49d1-950c-4f78aeffc21b}" removed="1"/>
